--- a/incidentes_mes.xlsx
+++ b/incidentes_mes.xlsx
@@ -1,28 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LuisAlvaroRojasRinco\Desktop\AutInforme-py\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LuisAlvaroRojasRinco\Desktop\AutInforme-py\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC563DE-181A-45E3-9ECB-C93DCC58B975}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724B9899-AB85-4789-A3EA-8EB4AB3B6FA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="IncidentesSOC" sheetId="1" r:id="rId1"/>
+    <sheet name="Incidentes" sheetId="1" r:id="rId1"/>
+    <sheet name="Novedades" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
-  <si>
-    <t>Incidente</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="21">
+  <si>
+    <t>Codigo</t>
   </si>
   <si>
     <t>Agencia</t>
@@ -34,43 +35,76 @@
     <t>SUR1084</t>
   </si>
   <si>
+    <t>SUR1055</t>
+  </si>
+  <si>
+    <t>CAD4030</t>
+  </si>
+  <si>
+    <t>CRU7009</t>
+  </si>
+  <si>
+    <t>Malware</t>
+  </si>
+  <si>
     <t>SUR</t>
   </si>
   <si>
-    <t>Malware</t>
-  </si>
-  <si>
-    <t>SUR1055</t>
-  </si>
-  <si>
-    <t/>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>CRUE</t>
+  </si>
+  <si>
+    <t>CRU7032</t>
+  </si>
+  <si>
+    <t>Rasomware</t>
+  </si>
+  <si>
+    <t>TICKET: INC-16762.
+EVENTO: Falla en la Geolocalización operador Movistar.
+OBSERVACIONES: Se evidencia que no se esta recibiendo datos de geolocalización del Operador Movistar, los demás
+operadores se encuentran con normalidad</t>
+  </si>
+  <si>
+    <t>TICKET:INC-16290.
+EVENTO: Falla en la Geolocalización operador TIGO.
+OBSERVACIONES: Se evidencia que no se esta recibiendo datos de geolocalización del Operador TIGO, los demás operadores se encuentran con normalidad</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Novedades</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>ACTIVA</t>
+  </si>
+  <si>
+    <t>CERRADA</t>
+  </si>
+  <si>
+    <t>TICKET: INC-17118
+EVENTO: Falla ingreso de llamadas Vesta _x000B_OBSERVACIONES: Falla ingreso de llamadas Vesta  2HORA INICIO: 11:11pmHORA FIN: 2:03am
+HORA INICIO: 11:11pm
+HORA SOLUCION: 2:03am</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -81,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -89,51 +123,21 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -163,28 +167,28 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="0000FF"/>
@@ -227,7 +231,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -262,7 +265,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -286,6 +288,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -296,31 +299,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -342,7 +345,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -400,7 +403,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -413,12 +416,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -437,67 +441,159 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28819674-DB58-40C7-A1F4-2E58262327E5}">
+  <dimension ref="A1:E1048576"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="56.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="55.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1048575" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048575" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048576" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{1DC309E1-3454-4DE9-BC82-3EDC5FAD46CB}">
+      <formula1>$A$1048575:$A$1048576</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
